--- a/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/trdbondvaluationduration/TrdBondValuationDuration001.xlsx
+++ b/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/trdbondvaluationduration/TrdBondValuationDuration001.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>交易编号</t>
   </si>
@@ -30,7 +30,7 @@
     <t>资产简称</t>
   </si>
   <si>
-    <t>交易场所</t>
+    <t>交易类型</t>
   </si>
   <si>
     <t>交易日期</t>
@@ -39,16 +39,13 @@
     <t>会计分类</t>
   </si>
   <si>
-    <t>交易类型</t>
-  </si>
-  <si>
     <t>实收利息</t>
   </si>
   <si>
     <t>实收本金</t>
   </si>
   <si>
-    <t>计划支付日</t>
+    <t>计息结束日</t>
   </si>
   <si>
     <t>资金交收日</t>
@@ -60,7 +57,7 @@
     <t>币种</t>
   </si>
   <si>
-    <t>本币交易金额</t>
+    <t>交易金额</t>
   </si>
   <si>
     <t>资金账户</t>
@@ -92,16 +89,60 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -115,44 +156,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -166,17 +170,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -192,7 +219,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -201,36 +228,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -245,187 +242,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -436,6 +433,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -457,8 +478,19 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -487,30 +519,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -525,162 +533,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1047,28 +1044,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="16.8833333333333" customWidth="1"/>
-    <col min="2" max="2" width="13.2666666666667" customWidth="1"/>
-    <col min="3" max="3" width="11.075" customWidth="1"/>
-    <col min="4" max="4" width="19.0666666666667" customWidth="1"/>
-    <col min="5" max="5" width="12.1666666666667" customWidth="1"/>
-    <col min="6" max="6" width="11.725" customWidth="1"/>
-    <col min="7" max="7" width="12.1666666666667" customWidth="1"/>
-    <col min="8" max="8" width="14.4666666666667" customWidth="1"/>
-    <col min="9" max="9" width="9.85833333333333" style="2" customWidth="1"/>
-    <col min="10" max="10" width="10.3" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.875" customWidth="1"/>
-    <col min="12" max="12" width="11.0666666666667" customWidth="1"/>
-    <col min="13" max="13" width="13.15" customWidth="1"/>
-    <col min="14" max="14" width="11.175" customWidth="1"/>
-    <col min="15" max="15" width="16.1166666666667" customWidth="1"/>
-    <col min="16" max="16" width="13.8166666666667" customWidth="1"/>
+    <col min="1" max="1" width="18.0833333333333" customWidth="1"/>
+    <col min="2" max="2" width="17.3166666666667" customWidth="1"/>
+    <col min="3" max="3" width="19.6166666666667" customWidth="1"/>
+    <col min="4" max="4" width="21.9333333333333" customWidth="1"/>
+    <col min="5" max="5" width="19.25" customWidth="1"/>
+    <col min="6" max="6" width="14.1416666666667" customWidth="1"/>
+    <col min="7" max="7" width="16.7666666666667" customWidth="1"/>
+    <col min="8" max="8" width="13.2583333333333" customWidth="1"/>
+    <col min="9" max="9" width="13" style="2" customWidth="1"/>
+    <col min="10" max="10" width="11.8416666666667" style="2" customWidth="1"/>
+    <col min="11" max="11" width="15.3416666666667" customWidth="1"/>
+    <col min="12" max="14" width="12.3833333333333" customWidth="1"/>
+    <col min="15" max="15" width="14.1333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:16">
+    <row r="1" s="1" customFormat="1" spans="1:15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1090,13 +1084,13 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="4" t="s">
@@ -1113,9 +1107,6 @@
       </c>
       <c r="O1" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/trdbondvaluationduration/TrdBondValuationDuration001.xlsx
+++ b/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/trdbondvaluationduration/TrdBondValuationDuration001.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>交易编号</t>
   </si>
@@ -45,7 +45,7 @@
     <t>实收本金</t>
   </si>
   <si>
-    <t>计息结束日</t>
+    <t>计划支付日</t>
   </si>
   <si>
     <t>资金交收日</t>
@@ -55,9 +55,6 @@
   </si>
   <si>
     <t>币种</t>
-  </si>
-  <si>
-    <t>交易金额</t>
   </si>
   <si>
     <t>资金账户</t>
@@ -70,8 +67,8 @@
   <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
   </numFmts>
   <fonts count="21">
@@ -89,6 +86,59 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -97,7 +147,46 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -105,14 +194,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -126,37 +207,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -169,69 +229,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -242,91 +239,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -338,91 +419,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -433,30 +430,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -471,26 +444,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,7 +467,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -533,16 +486,60 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -551,133 +548,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1044,7 +1041,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18.0833333333333" customWidth="1"/>
@@ -1058,11 +1055,11 @@
     <col min="9" max="9" width="13" style="2" customWidth="1"/>
     <col min="10" max="10" width="11.8416666666667" style="2" customWidth="1"/>
     <col min="11" max="11" width="15.3416666666667" customWidth="1"/>
-    <col min="12" max="14" width="12.3833333333333" customWidth="1"/>
-    <col min="15" max="15" width="14.1333333333333" customWidth="1"/>
+    <col min="12" max="13" width="12.3833333333333" customWidth="1"/>
+    <col min="14" max="14" width="14.1333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:15">
+    <row r="1" s="1" customFormat="1" spans="1:14">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1104,9 +1101,6 @@
       </c>
       <c r="N1" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/trdbondvaluationduration/TrdBondValuationDuration001.xlsx
+++ b/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/trdbondvaluationduration/TrdBondValuationDuration001.xlsx
@@ -45,7 +45,7 @@
     <t>实收本金</t>
   </si>
   <si>
-    <t>计划支付日</t>
+    <t>计息结束日</t>
   </si>
   <si>
     <t>资金交收日</t>
@@ -65,11 +65,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -86,17 +86,98 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -110,123 +191,42 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -239,6 +239,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -251,55 +281,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -311,115 +365,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -430,6 +430,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -472,17 +487,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -494,6 +503,15 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -512,34 +530,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -548,133 +548,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1053,9 +1053,10 @@
     <col min="7" max="7" width="16.7666666666667" customWidth="1"/>
     <col min="8" max="8" width="13.2583333333333" customWidth="1"/>
     <col min="9" max="9" width="13" style="2" customWidth="1"/>
-    <col min="10" max="10" width="11.8416666666667" style="2" customWidth="1"/>
-    <col min="11" max="11" width="15.3416666666667" customWidth="1"/>
-    <col min="12" max="13" width="12.3833333333333" customWidth="1"/>
+    <col min="10" max="10" width="11.9416666666667" style="2" customWidth="1"/>
+    <col min="11" max="11" width="13.7083333333333" customWidth="1"/>
+    <col min="12" max="12" width="12.3833333333333" customWidth="1"/>
+    <col min="13" max="13" width="15.3416666666667" customWidth="1"/>
     <col min="14" max="14" width="14.1333333333333" customWidth="1"/>
   </cols>
   <sheetData>

--- a/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/trdbondvaluationduration/TrdBondValuationDuration001.xlsx
+++ b/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/trdbondvaluationduration/TrdBondValuationDuration001.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>交易编号</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>资金账户</t>
+  </si>
+  <si>
+    <t>数据来源</t>
   </si>
 </sst>
 </file>
@@ -65,11 +68,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -87,59 +90,75 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -153,6 +172,59 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -160,75 +232,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -239,187 +242,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -430,21 +433,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -459,6 +447,24 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -480,38 +486,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -530,16 +509,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -548,133 +551,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1041,7 +1044,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18.0833333333333" customWidth="1"/>
@@ -1060,7 +1063,7 @@
     <col min="14" max="14" width="14.1333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:14">
+    <row r="1" s="1" customFormat="1" spans="1:15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1102,6 +1105,9 @@
       </c>
       <c r="N1" s="4" t="s">
         <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/trdbondvaluationduration/TrdBondValuationDuration001.xlsx
+++ b/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/trdbondvaluationduration/TrdBondValuationDuration001.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>交易编号</t>
   </si>
@@ -33,22 +33,19 @@
     <t>交易类型</t>
   </si>
   <si>
-    <t>交易日期</t>
-  </si>
-  <si>
     <t>会计分类</t>
   </si>
   <si>
+    <t>计息结束日</t>
+  </si>
+  <si>
+    <t>资金到账日</t>
+  </si>
+  <si>
     <t>实收利息</t>
   </si>
   <si>
     <t>实收本金</t>
-  </si>
-  <si>
-    <t>计息结束日</t>
-  </si>
-  <si>
-    <t>资金交收日</t>
   </si>
   <si>
     <t>结算金额</t>
@@ -68,11 +65,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -90,12 +87,27 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -103,8 +115,61 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -113,13 +178,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -150,21 +208,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
@@ -172,54 +215,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,37 +239,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -284,102 +401,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -392,37 +419,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -433,6 +430,54 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -447,15 +492,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -494,55 +530,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -551,137 +548,137 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -694,6 +691,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1044,7 +1044,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18.0833333333333" customWidth="1"/>
@@ -1052,18 +1052,17 @@
     <col min="3" max="3" width="19.6166666666667" customWidth="1"/>
     <col min="4" max="4" width="21.9333333333333" customWidth="1"/>
     <col min="5" max="5" width="19.25" customWidth="1"/>
-    <col min="6" max="6" width="14.1416666666667" customWidth="1"/>
-    <col min="7" max="7" width="16.7666666666667" customWidth="1"/>
-    <col min="8" max="8" width="13.2583333333333" customWidth="1"/>
-    <col min="9" max="9" width="13" style="2" customWidth="1"/>
-    <col min="10" max="10" width="11.9416666666667" style="2" customWidth="1"/>
-    <col min="11" max="11" width="13.7083333333333" customWidth="1"/>
-    <col min="12" max="12" width="12.3833333333333" customWidth="1"/>
-    <col min="13" max="13" width="15.3416666666667" customWidth="1"/>
-    <col min="14" max="14" width="14.1333333333333" customWidth="1"/>
+    <col min="6" max="6" width="16.7666666666667" customWidth="1"/>
+    <col min="7" max="7" width="13.2583333333333" customWidth="1"/>
+    <col min="8" max="8" width="13" style="2" customWidth="1"/>
+    <col min="9" max="9" width="11.9416666666667" style="2" customWidth="1"/>
+    <col min="10" max="10" width="13.7083333333333" customWidth="1"/>
+    <col min="11" max="11" width="12.3833333333333" customWidth="1"/>
+    <col min="12" max="12" width="15.3416666666667" customWidth="1"/>
+    <col min="13" max="13" width="14.1333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:15">
+    <row r="1" s="1" customFormat="1" spans="1:14">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1082,16 +1081,16 @@
       <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="4" t="s">
@@ -1103,11 +1102,8 @@
       <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
